--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/sumario_modelos.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2003_2014/tabelas/sumario_modelos.xlsx
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>-55.42632474858539</v>
+        <v>-55.42632474858538</v>
       </c>
       <c r="F2" t="n">
-        <v>-52.65783884252224</v>
+        <v>-52.65783884252222</v>
       </c>
       <c r="G2" t="n">
-        <v>-54.30132445294528</v>
+        <v>-54.30132445294527</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -506,13 +506,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>-53.19179284102158</v>
+        <v>-53.19179284102159</v>
       </c>
       <c r="F3" t="n">
         <v>-50.42330693495843</v>
       </c>
       <c r="G3" t="n">
-        <v>-52.06679254538147</v>
+        <v>-52.06679254538148</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -536,13 +536,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-54.83546057296861</v>
+        <v>-54.83546057296862</v>
       </c>
       <c r="F4" t="n">
         <v>-52.06697466690547</v>
       </c>
       <c r="G4" t="n">
-        <v>-53.71046027732851</v>
+        <v>-53.71046027732852</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -566,13 +566,13 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>-53.14740236644004</v>
+        <v>-53.14740236644005</v>
       </c>
       <c r="F5" t="n">
         <v>-48.29369236913469</v>
       </c>
       <c r="G5" t="n">
-        <v>-51.17499979092874</v>
+        <v>-51.17499979092875</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -626,10 +626,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>-50.25528562987192</v>
+        <v>-50.25528562987191</v>
       </c>
       <c r="F7" t="n">
-        <v>-47.48679972380877</v>
+        <v>-47.48679972380876</v>
       </c>
       <c r="G7" t="n">
         <v>-49.13028533423181</v>
